--- a/data/invoices_database.xlsx
+++ b/data/invoices_database.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,9 +486,24 @@
           <t>午後の紅茶オレンジ, 午後の紅茶白ぶどう, ほろよいマスカット, ほろよいマスカット, ほろよいベリー</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>638</t>
+      <c r="C4" t="n">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2025.11.30</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ONE室内飼い猫用1歳サ-モ, * カップN トムヤムクン 2コX単188, * イマイBONチチャ口, レシ袋 L, ONE室内飼い猫用1歳チキ, * 王老吉, * 海底捞 トマト麻辣湯</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>6168</t>
         </is>
       </c>
     </row>
